--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488262_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488262_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. VARO BARBANCHO</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0716</v>
+        <v>2.3585</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1471</v>
+        <v>2.9519</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.5935</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5369</v>
+        <v>4.4839</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6129</v>
+        <v>-0.2512</v>
       </c>
       <c r="I2" t="n">
-        <v>4.924</v>
+        <v>4.7351</v>
       </c>
       <c r="J2" t="n">
-        <v>8.1471</v>
+        <v>4.9852</v>
       </c>
       <c r="K2" t="n">
-        <v>2.847</v>
+        <v>0.4422</v>
       </c>
       <c r="L2" t="n">
-        <v>5.3001</v>
+        <v>4.543</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6102</v>
+        <v>-0.5012</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2341</v>
+        <v>-0.6934</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3761</v>
+        <v>0.1922</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.1499</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.6322</v>
+        <v>-1.8529</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3154</v>
+        <v>0.3013</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3679</v>
+        <v>0.1346</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0525</v>
+        <v>0.1666</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0.9444</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>J. VARO BARBANCHO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4554</v>
+        <v>2.2888</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5188</v>
+        <v>2.9305</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0635</v>
+        <v>-0.6417</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6314</v>
+        <v>5.5369</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9464</v>
+        <v>0.6129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3149</v>
+        <v>4.924</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8977</v>
+        <v>8.1471</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7519</v>
+        <v>2.847</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1458</v>
+        <v>5.3001</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2663</v>
+        <v>-2.6102</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1944</v>
+        <v>-2.2341</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4607</v>
+        <v>-0.3761</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1853</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9264</v>
+        <v>-4.6322</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6208</v>
+        <v>-0.0982</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7113</v>
+        <v>-0.5844</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0905</v>
+        <v>0.4862</v>
       </c>
       <c r="V3" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3529</v>
+        <v>1.9456</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2664</v>
+        <v>1.9105</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9136</v>
+        <v>0.035</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4839</v>
+        <v>1.6314</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2512</v>
+        <v>1.9464</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7351</v>
+        <v>-0.3149</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9852</v>
+        <v>1.8977</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4422</v>
+        <v>1.7519</v>
       </c>
       <c r="L4" t="n">
-        <v>4.543</v>
+        <v>0.1458</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5012</v>
+        <v>-0.2663</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6934</v>
+        <v>0.1944</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1922</v>
+        <v>-0.4607</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.4823</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7043</v>
+        <v>-0.1306</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.3196</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1535</v>
+        <v>0.189</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9444</v>
+        <v>0.63</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.315</v>
+        <v>1.2589</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6294</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SHANNON</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3422</v>
+        <v>-0.2566</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8631</v>
+        <v>0.0917</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5209</v>
+        <v>-0.3483</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2912</v>
+        <v>-1.0945</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0929</v>
+        <v>-0.7857</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1983</v>
+        <v>-0.3088</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9437</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.824</v>
+        <v>0.0644</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1197</v>
+        <v>-0.5699</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6525</v>
+        <v>-0.589</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7311</v>
+        <v>-0.8501</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9214</v>
+        <v>0.2611</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.2234</v>
+        <v>0.7411</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3306</v>
+        <v>0.4107</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7549</v>
+        <v>0.5972</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5757</v>
+        <v>-0.1865</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9439</v>
+        <v>-0.3139</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>J. SHANNON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.11</v>
+        <v>-0.6875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5814</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4714</v>
+        <v>-0.7671</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0945</v>
+        <v>0.2912</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7857</v>
+        <v>0.0929</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3088</v>
+        <v>0.1983</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5054999999999999</v>
+        <v>1.9437</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0644</v>
+        <v>0.824</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5699</v>
+        <v>1.1197</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.589</v>
+        <v>-1.6525</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8501</v>
+        <v>-0.7311</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2611</v>
+        <v>-0.9214</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7411</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7772</v>
+        <v>0.3009</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0869</v>
+        <v>-0.0286</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3096</v>
+        <v>0.3295</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3139</v>
+        <v>0.9439</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8519</v>
+        <v>-3.2945</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8915999999999999</v>
+        <v>-0.9895</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9603</v>
+        <v>-2.305</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4727</v>
@@ -1000,13 +1000,13 @@
         <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8061</v>
+        <v>0.3634</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3209</v>
+        <v>0.2229</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4852</v>
+        <v>0.1405</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2589</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2815</v>
+        <v>-3.9866</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0129</v>
+        <v>-2.915</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2686</v>
+        <v>-1.0717</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6621</v>
@@ -1078,13 +1078,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0095</v>
+        <v>0.3044</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1716</v>
+        <v>-0.0736</v>
       </c>
       <c r="U8" t="n">
-        <v>0.181</v>
+        <v>0.378</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2583</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.946</v>
+        <v>-5.0669</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7059</v>
+        <v>-4.0976</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2401</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0864</v>
@@ -1156,13 +1156,13 @@
         <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6233</v>
+        <v>0.5024</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4303</v>
+        <v>0.0386</v>
       </c>
       <c r="U9" t="n">
-        <v>0.193</v>
+        <v>0.4638</v>
       </c>
       <c r="V9" t="n">
         <v>-0.63</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0733</v>
+        <v>-5.1214</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7308</v>
+        <v>-2.9267</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3425</v>
+        <v>-2.1947</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4898</v>
@@ -1234,13 +1234,13 @@
         <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6004</v>
+        <v>-0.6485</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0584</v>
+        <v>-0.2543</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5419</v>
+        <v>-0.3942</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3155</v>
@@ -1270,25 +1270,25 @@
         <v>-11.8206</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9644</v>
+        <v>-2.964499999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.856299999999999</v>
+        <v>-8.856300000000001</v>
       </c>
       <c r="G11" t="n">
         <v>1.137900000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.616099999999999</v>
+        <v>-7.616100000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>8.754</v>
+        <v>8.754000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>14.2604</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8577</v>
+        <v>2.857700000000001</v>
       </c>
       <c r="L11" t="n">
         <v>11.4026</v>
@@ -1315,7 +1315,7 @@
         <v>1.3058</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2670999999999999</v>
+        <v>-0.2672000000000001</v>
       </c>
       <c r="U11" t="n">
         <v>1.5729</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CASTILLO ORTEGA</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.508599999999999</v>
+        <v>6.2321</v>
       </c>
       <c r="E12" t="n">
-        <v>7.0948</v>
+        <v>5.5221</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4138</v>
+        <v>0.71</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5224</v>
+        <v>4.9984</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2916</v>
+        <v>2.963</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2307</v>
+        <v>2.0354</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5243</v>
+        <v>6.0004</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6949</v>
+        <v>3.3663</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8294</v>
+        <v>2.6341</v>
       </c>
       <c r="M12" t="n">
         <v>-1.0019</v>
@@ -1381,37 +1381,37 @@
         <v>-0.5987</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1499</v>
+        <v>2.2234</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R12" t="n">
         <v>3.1499</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2063</v>
+        <v>-0.3603</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3116</v>
+        <v>-0.1812</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1052</v>
+        <v>-0.1791</v>
       </c>
       <c r="V12" t="n">
-        <v>0.63</v>
+        <v>-0.6294</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2589</v>
+        <v>0.6294</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>A. CASTILLO ORTEGA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2287</v>
+        <v>6.0844</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4449</v>
+        <v>4.7445</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7838000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="G13" t="n">
-        <v>4.9984</v>
+        <v>1.5224</v>
       </c>
       <c r="H13" t="n">
-        <v>2.963</v>
+        <v>1.2916</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0354</v>
+        <v>0.2307</v>
       </c>
       <c r="J13" t="n">
-        <v>6.0004</v>
+        <v>2.5243</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3663</v>
+        <v>1.6949</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6341</v>
+        <v>0.8294</v>
       </c>
       <c r="M13" t="n">
         <v>-1.0019</v>
@@ -1459,31 +1459,31 @@
         <v>-0.5987</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2234</v>
+        <v>3.1499</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>3.1499</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3637</v>
+        <v>0.7822</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2584</v>
+        <v>0.9613</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1052</v>
+        <v>-0.1791</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6294</v>
+        <v>0.63</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6294</v>
+        <v>1.2589</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1594</v>
+        <v>5.6491</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4178</v>
+        <v>4.9074</v>
       </c>
       <c r="F14" t="n">
         <v>0.7416</v>
@@ -1546,10 +1546,10 @@
         <v>2.7793</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1729</v>
+        <v>0.3168</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4961</v>
+        <v>-0.0065</v>
       </c>
       <c r="U14" t="n">
         <v>0.3233</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3221</v>
+        <v>0.5518</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3221</v>
+        <v>-0.6017</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.1536</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3221</v>
+        <v>-1.4109</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3221</v>
+        <v>-0.8426</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-0.5683</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3221</v>
+        <v>-0.1474</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3221</v>
+        <v>-0.2623</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-1.2635</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.5803</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.6833</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.221</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.1576</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.0634</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.045</v>
+        <v>0.4859</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4352</v>
+        <v>-1.0435</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4802</v>
+        <v>1.5294</v>
       </c>
       <c r="G16" t="n">
         <v>0.0011</v>
@@ -1702,13 +1702,13 @@
         <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3823</v>
+        <v>-0.9414</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9302</v>
+        <v>-0.5384</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4522</v>
+        <v>-0.4029</v>
       </c>
       <c r="V16" t="n">
         <v>0.3144</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1102</v>
+        <v>0.3221</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0914</v>
+        <v>0.3221</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9812</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4109</v>
+        <v>0.3221</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8426</v>
+        <v>0.3221</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5683</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1474</v>
+        <v>0.3221</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2623</v>
+        <v>0.3221</v>
       </c>
       <c r="L17" t="n">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2635</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5803</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6833</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.441</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.332</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.109</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3056</v>
+        <v>0.0386</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1041</v>
+        <v>0.2021</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4097</v>
+        <v>-0.1635</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7184</v>
@@ -1858,13 +1858,13 @@
         <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2547</v>
+        <v>-0.9106</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.766</v>
+        <v>-0.6681</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4887</v>
+        <v>-0.2425</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7645</v>
+        <v>-0.7892</v>
       </c>
       <c r="E19" t="n">
         <v>-0.7398</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0247</v>
+        <v>-0.0493</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2281</v>
@@ -1936,13 +1936,13 @@
         <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>0.093</v>
+        <v>0.0684</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1641</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2572</v>
+        <v>0.2325</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4714</v>
+        <v>-1.3237</v>
       </c>
       <c r="E20" t="n">
         <v>-0.4624</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0091</v>
+        <v>-0.8613</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9272</v>
@@ -2014,13 +2014,13 @@
         <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1562</v>
+        <v>-1.0085</v>
       </c>
       <c r="T20" t="n">
         <v>-0.6019</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5544</v>
+        <v>-0.4066</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3144</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8044</v>
+        <v>-1.585</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6445</v>
+        <v>-1.2528</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1599</v>
+        <v>-0.3322</v>
       </c>
       <c r="G21" t="n">
         <v>-4.5203</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0813</v>
+        <v>0.138</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9302</v>
+        <v>-0.5384</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8488</v>
+        <v>0.6765</v>
       </c>
       <c r="V21" t="n">
         <v>0.9444</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.987</v>
+        <v>-3.8455</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1541</v>
+        <v>-2.7417</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.833</v>
+        <v>-1.1038</v>
       </c>
       <c r="G22" t="n">
         <v>-4.1779</v>
@@ -2170,13 +2170,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>1.247</v>
+        <v>0.3886</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5944</v>
+        <v>0.0069</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6526</v>
+        <v>0.3818</v>
       </c>
       <c r="V22" t="n">
         <v>0.3144</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>11.8207</v>
+        <v>11.8206</v>
       </c>
       <c r="E23" t="n">
-        <v>8.856299999999997</v>
+        <v>8.856299999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>2.9642</v>
+        <v>2.9645</v>
       </c>
       <c r="G23" t="n">
         <v>-1.137799999999999</v>
@@ -2251,10 +2251,10 @@
         <v>-1.3058</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.5729</v>
+        <v>-1.5728</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2672</v>
+        <v>0.2673</v>
       </c>
       <c r="V23" t="n">
         <v>3.1472</v>
